--- a/Result/profitability/1301.xlsx
+++ b/Result/profitability/1301.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.22</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.03625</v>
+        <v>0.23375</v>
       </c>
       <c r="N2" t="n">
-        <v>4.8175</v>
+        <v>5.7825</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -690,7 +690,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>2.32</v>
       </c>
       <c r="M3" t="n">
-        <v>0.315</v>
+        <v>0.5187499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>5.79</v>
+        <v>6.85375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>2.46</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6174999999999999</v>
+        <v>0.825</v>
       </c>
       <c r="N4" t="n">
-        <v>6.5525</v>
+        <v>7.482500000000001</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-2.55</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2975</v>
+        <v>0.63625</v>
       </c>
       <c r="N5" t="n">
-        <v>3.605</v>
+        <v>4.748749999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.51</v>
       </c>
       <c r="M6" t="n">
-        <v>0.49125</v>
+        <v>0.71125</v>
       </c>
       <c r="N6" t="n">
-        <v>4.39625</v>
+        <v>5.805</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.26</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6599999999999999</v>
+        <v>0.925</v>
       </c>
       <c r="N7" t="n">
-        <v>6.102499999999999</v>
+        <v>7.38625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.5</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9037500000000001</v>
+        <v>1.04875</v>
       </c>
       <c r="N8" t="n">
-        <v>7.37125</v>
+        <v>8.49</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>1.93</v>
       </c>
       <c r="M11" t="n">
-        <v>0.96375</v>
+        <v>0.9637500000000001</v>
       </c>
       <c r="N11" t="n">
         <v>9.286249999999999</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>47254</v>
+      </c>
+      <c r="D75" t="n">
+        <v>41274</v>
+      </c>
+      <c r="E75" t="n">
+        <v>5980</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2880</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.09%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>7977</v>
+      </c>
+      <c r="J75" t="n">
+        <v>10857</v>
+      </c>
+      <c r="K75" t="n">
+        <v>10652</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.01999999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>4.73625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.274509803921569</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>2.418918918918919</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.605769230769231</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>2.614285714285714</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
